--- a/_docs_/trim02/03_estimación_costos/Control_Store_Scrum_DE.xlsx
+++ b/_docs_/trim02/03_estimación_costos/Control_Store_Scrum_DE.xlsx
@@ -65,7 +65,7 @@
     <t>Brayan Torres</t>
   </si>
   <si>
-    <t>Líder técnico · Frontend React · API REST · Despliegue</t>
+    <t>Líder técnico · Frontend web (Blade + Bootstrap) · API REST · Despliegue</t>
   </si>
   <si>
     <t>DO</t>
@@ -158,7 +158,7 @@
     <t>2.1</t>
   </si>
   <si>
-    <t>Hosting frontend — Render Static Site</t>
+    <t>Hosting web (Laravel + Blade) — Railway</t>
   </si>
   <si>
     <t>6 meses</t>
@@ -176,7 +176,7 @@
     <t>2.2</t>
   </si>
   <si>
-    <t>Hosting backend — Render Web Service</t>
+    <t>Hosting API REST (Laravel) — Railway</t>
   </si>
   <si>
     <t>Gratis. Se duerme tras 15 min sin tráfico</t>
@@ -185,7 +185,7 @@
     <t>2.3</t>
   </si>
   <si>
-    <t>Base de datos — Supabase PostgreSQL</t>
+    <t>Base de datos - MySQL 8</t>
   </si>
   <si>
     <t>Gratis. Uso comercial permitido, 500 MB</t>
@@ -506,10 +506,10 @@
     <t>Reunión Sprint Review + Retro + Cliente — Cierre Módulo 2 (Ago)</t>
   </si>
   <si>
-    <t>Frontend base en React y configuración de rutas</t>
-  </si>
-  <si>
-    <t>Script DML, autenticación JWT y seguridad con bcrypt</t>
+    <t>Frontend base en Blade + Bootstrap y configuración de rutas</t>
+  </si>
+  <si>
+    <t>Script DML, autenticación con Laravel Sanctum y seguridad con bcrypt</t>
   </si>
   <si>
     <t>Diseño de componentes UI y configuración de pruebas unitarias</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">  Equipos YA SON PROPIEDAD de cada integrante. Se incluye depreciación real por uso en el proyecto (116 días).</t>
   </si>
   <si>
-    <t xml:space="preserve">  BT — Brayan Torres  |  Líder técnico · Frontend React · API REST · Despliegue</t>
+    <t xml:space="preserve">  BT — Brayan Torres  |  Líder técnico · Frontend web (Blade + Bootstrap) · API REST · Despliegue</t>
   </si>
   <si>
     <t>COMPONENTE</t>
@@ -743,10 +743,10 @@
     <t>LÍMITES Y NOTAS</t>
   </si>
   <si>
-    <t>Frontend (React)</t>
-  </si>
-  <si>
-    <t>Render — Static Site</t>
+    <t>Frontend (Blade + Bootstrap 5)</t>
+  </si>
+  <si>
+    <t>Railway — Web Service</t>
   </si>
   <si>
     <t>Free</t>
@@ -755,10 +755,10 @@
     <t>Sin 'sleep', uso comercial permitido. HTTPS y CDN incluidos.</t>
   </si>
   <si>
-    <t>Backend (API REST Node.js)</t>
-  </si>
-  <si>
-    <t>Render — Web Service</t>
+    <t>Backend (API REST Laravel 11)</t>
+  </si>
+  <si>
+    <t>Railway — Web Service</t>
   </si>
   <si>
     <t>Se 'duerme' tras 15 min sin tráfico (despierta en 30-60s).</t>
@@ -767,7 +767,7 @@
     <t>Base de Datos</t>
   </si>
   <si>
-    <t>Supabase — PostgreSQL</t>
+    <t>MySQL 8</t>
   </si>
   <si>
     <t>500 MB · uso comercial permitido · pausa tras 7 días sin actividad.</t>
@@ -824,7 +824,7 @@
     <t>Backend sin 'sleep' 24/7</t>
   </si>
   <si>
-    <t>Render Starter</t>
+    <t>Railway Hobby</t>
   </si>
   <si>
     <t>$7 USD</t>
@@ -845,10 +845,10 @@
     <t>Plan con $5 USD de crédito mensual incluido.</t>
   </si>
   <si>
-    <t>• Vercel es gratis, pero prohíbe uso comercial en su plan Hobby — por eso se eligió Render.</t>
-  </si>
-  <si>
-    <t>• Supabase sí permite uso comercial gratis — opción correcta para la BD de un negocio real.</t>
+    <t>• Vercel y Netlify solo sirven sitios estáticos y no ejecutan PHP — por eso se eligió Railway.</t>
+  </si>
+  <si>
+    <t>• Railway ofrece MySQL 8 gestionado con backups automáticos — opción correcta para la BD de un negocio real.</t>
   </si>
   <si>
     <t xml:space="preserve">  Control Store  |  Recursos Humanos — Equipo Real  |  3 Desarrolladores Junior ADSO SENA</t>
@@ -950,7 +950,7 @@
     <t>6.1</t>
   </si>
   <si>
-    <t>Despliegue en Render/Vercel y configuración del dominio</t>
+    <t>Despliegue en Railway y configuración del dominio</t>
   </si>
   <si>
     <t>8%</t>
@@ -1118,7 +1118,7 @@
     <t>Desarrollador Full Stack — Líder Técnico</t>
   </si>
   <si>
-    <t>React · Node.js/Django · API REST · Despliegue</t>
+    <t>Laravel 11 · PHP + MySQL 8 · API REST · Despliegue</t>
   </si>
   <si>
     <t>Colpatria EPS</t>
@@ -1142,7 +1142,7 @@
     <t>Desarrollador Full Stack — Backend &amp; Base de Datos</t>
   </si>
   <si>
-    <t>Backend · PostgreSQL · Seguridad · Documentación ISO</t>
+    <t>Backend · MySQL 8 · Seguridad · Documentación ISO</t>
   </si>
   <si>
     <t>Desarrollador Full Stack — UI/UX &amp; Calidad</t>
@@ -1392,7 +1392,7 @@
     <t xml:space="preserve">  SPRINT 1 — Módulo de Usuarios   |   01/07/2026 – 17/07/2026   |   3 semanas</t>
   </si>
   <si>
-    <t xml:space="preserve">  Sprint Goal: EP-01 · RF01–RF07 con autenticación JWT + bcrypt</t>
+    <t xml:space="preserve">  Sprint Goal: EP-01 · RF01–RF07 con autenticación con Laravel Sanctum + bcrypt</t>
   </si>
   <si>
     <t>SPRINT 1</t>
@@ -1407,7 +1407,7 @@
     <t>RF01</t>
   </si>
   <si>
-    <t>Iniciar sesión (autenticación JWT + roles)</t>
+    <t>Iniciar sesión (autenticación con Laravel Sanctum + roles)</t>
   </si>
   <si>
     <t>▬</t>
@@ -2103,7 +2103,7 @@
     <t>T-6.3</t>
   </si>
   <si>
-    <t>Despliegue Render/Supabase</t>
+    <t>Despliegue Railway (Laravel + MySQL)</t>
   </si>
   <si>
     <t>T-6.4</t>
@@ -2190,7 +2190,7 @@
     <t>SP</t>
   </si>
   <si>
-    <t>Iniciar sesión — autenticación JWT con roles ADMIN/VENDEDOR/DOMICILIARIO</t>
+    <t>Iniciar sesión — autenticación con Laravel Sanctum con roles ADMIN/VENDEDOR/DOMICILIARIO</t>
   </si>
   <si>
     <t>Login exitoso redirige al dashboard del rol; credenciales incorrectas muestran error; usuario inactivo bloqueado</t>
@@ -2337,7 +2337,7 @@
     <t>INCLUDE: Guardar producto en base de datos de inventario</t>
   </si>
   <si>
-    <t>Registro persistido en PostgreSQL</t>
+    <t>Registro persistido en MySQL 8</t>
   </si>
   <si>
     <t>EXTEND: Error si código de barras ya existe (duplicado)</t>
@@ -2385,7 +2385,7 @@
     <t>INCLUDE: Guardar cambios del producto en BD</t>
   </si>
   <si>
-    <t>Datos actualizados en PostgreSQL</t>
+    <t>Datos actualizados en MySQL 8</t>
   </si>
   <si>
     <t>INCLUDE: Registrar log de auditoría por cada cambio</t>
@@ -2812,7 +2812,7 @@
     <t>HECHO</t>
   </si>
   <si>
-    <t>Iniciar sesión (JWT + roles)</t>
+    <t>Iniciar sesión (Sanctum + roles)</t>
   </si>
   <si>
     <t>INCLUDE: Validar credenciales en BD</t>
@@ -3315,7 +3315,7 @@
     <t>INSTRUCTOR SENA — Supervisor Académico (Product Owner delegado)</t>
   </si>
   <si>
-    <t>Brayan Torres — Frontend React · API R</t>
+    <t>Brayan Torres — Frontend web (Blade + Bootstrap) · API R</t>
   </si>
   <si>
     <t xml:space="preserve">David Ortegón — Base de Datos · Backend · Seguridad </t>
